--- a/web/public/forms/gy-jajae.xlsx
+++ b/web/public/forms/gy-jajae.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자재 구매계약서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'자재 구매계약서'!$A$1:$X$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'자재 구매계약서'!$A$1:$X$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;원 (부가세 포함)&quot;;;&quot;&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0##%"/>
+    <numFmt numFmtId="167" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0.###;[Red]-#,##0.###;&quot;&quot;"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,32 +40,59 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +101,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00EEF4FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1B8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EEF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6F8FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +135,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,40 +160,87 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="300" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -504,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X61"/>
+  <dimension ref="A1:X69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" min="1" max="1"/>
@@ -533,15 +631,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -565,7 +663,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -595,7 +693,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -625,7 +723,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="7" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -655,7 +753,10 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="8">
+        <f>IF(SUM(S15:S19)=0,"",SUM(S15:S19)+K9)</f>
+        <v/>
+      </c>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -685,11 +786,16 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="9" t="n">
+        <v>0.1</v>
+      </c>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
+      <c r="K9" s="10">
+        <f>IF(SUM(S15:S19)=0,"",INT(ROUND(SUM(S15:S19)*G9,6)))</f>
+        <v/>
+      </c>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="5" t="n"/>
       <c r="N9" s="5" t="n"/>
@@ -715,7 +821,7 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
@@ -745,7 +851,7 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
@@ -775,7 +881,7 @@
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="n"/>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
@@ -796,7 +902,7 @@
     </row>
     <row r="13" ht="6" customHeight="1"/>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>품명</t>
         </is>
@@ -806,7 +912,7 @@
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>규격</t>
         </is>
@@ -815,33 +921,33 @@
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="5" t="n"/>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="L14" s="11" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
       <c r="M14" s="5" t="n"/>
-      <c r="N14" s="7" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
       <c r="O14" s="5" t="n"/>
-      <c r="P14" s="7" t="inlineStr">
+      <c r="P14" s="11" t="inlineStr">
         <is>
           <t>단가</t>
         </is>
       </c>
       <c r="Q14" s="5" t="n"/>
       <c r="R14" s="5" t="n"/>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="11" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
       <c r="T14" s="5" t="n"/>
       <c r="U14" s="5" t="n"/>
-      <c r="V14" s="7" t="inlineStr">
+      <c r="V14" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -850,523 +956,1675 @@
       <c r="X14" s="5" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr"/>
+      <c r="A15" s="12" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="8" t="inlineStr"/>
+      <c r="G15" s="13" t="n"/>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
       <c r="K15" s="5" t="n"/>
-      <c r="L15" s="8" t="inlineStr"/>
+      <c r="L15" s="13" t="n"/>
       <c r="M15" s="5" t="n"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="14" t="n"/>
       <c r="O15" s="5" t="n"/>
-      <c r="P15" s="8" t="inlineStr"/>
+      <c r="P15" s="15" t="n"/>
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
-      <c r="S15" s="8" t="inlineStr"/>
+      <c r="S15" s="10">
+        <f>IF(OR(N15="",P15=""),"",INT(ROUND(N15*P15,6)))</f>
+        <v/>
+      </c>
       <c r="T15" s="5" t="n"/>
       <c r="U15" s="5" t="n"/>
-      <c r="V15" s="8" t="inlineStr"/>
+      <c r="V15" s="13" t="n"/>
       <c r="W15" s="5" t="n"/>
       <c r="X15" s="5" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="inlineStr"/>
+      <c r="A16" s="12" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="8" t="inlineStr"/>
+      <c r="G16" s="13" t="n"/>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
       <c r="K16" s="5" t="n"/>
-      <c r="L16" s="8" t="inlineStr"/>
+      <c r="L16" s="13" t="n"/>
       <c r="M16" s="5" t="n"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="14" t="n"/>
       <c r="O16" s="5" t="n"/>
-      <c r="P16" s="8" t="inlineStr"/>
+      <c r="P16" s="15" t="n"/>
       <c r="Q16" s="5" t="n"/>
       <c r="R16" s="5" t="n"/>
-      <c r="S16" s="8" t="inlineStr"/>
+      <c r="S16" s="10">
+        <f>IF(OR(N16="",P16=""),"",INT(ROUND(N16*P16,6)))</f>
+        <v/>
+      </c>
       <c r="T16" s="5" t="n"/>
       <c r="U16" s="5" t="n"/>
-      <c r="V16" s="8" t="inlineStr"/>
+      <c r="V16" s="13" t="n"/>
       <c r="W16" s="5" t="n"/>
       <c r="X16" s="5" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="8" t="inlineStr"/>
+      <c r="A17" s="12" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="8" t="inlineStr"/>
+      <c r="G17" s="13" t="n"/>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="5" t="n"/>
-      <c r="L17" s="8" t="inlineStr"/>
+      <c r="L17" s="13" t="n"/>
       <c r="M17" s="5" t="n"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="14" t="n"/>
       <c r="O17" s="5" t="n"/>
-      <c r="P17" s="8" t="inlineStr"/>
+      <c r="P17" s="15" t="n"/>
       <c r="Q17" s="5" t="n"/>
       <c r="R17" s="5" t="n"/>
-      <c r="S17" s="8" t="inlineStr"/>
+      <c r="S17" s="10">
+        <f>IF(OR(N17="",P17=""),"",INT(ROUND(N17*P17,6)))</f>
+        <v/>
+      </c>
       <c r="T17" s="5" t="n"/>
       <c r="U17" s="5" t="n"/>
-      <c r="V17" s="8" t="inlineStr"/>
+      <c r="V17" s="13" t="n"/>
       <c r="W17" s="5" t="n"/>
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr"/>
+      <c r="A18" s="12" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="8" t="inlineStr"/>
+      <c r="G18" s="13" t="n"/>
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
       <c r="K18" s="5" t="n"/>
-      <c r="L18" s="8" t="inlineStr"/>
+      <c r="L18" s="13" t="n"/>
       <c r="M18" s="5" t="n"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="14" t="n"/>
       <c r="O18" s="5" t="n"/>
-      <c r="P18" s="8" t="inlineStr"/>
+      <c r="P18" s="15" t="n"/>
       <c r="Q18" s="5" t="n"/>
       <c r="R18" s="5" t="n"/>
-      <c r="S18" s="8" t="inlineStr"/>
+      <c r="S18" s="10">
+        <f>IF(OR(N18="",P18=""),"",INT(ROUND(N18*P18,6)))</f>
+        <v/>
+      </c>
       <c r="T18" s="5" t="n"/>
       <c r="U18" s="5" t="n"/>
-      <c r="V18" s="8" t="inlineStr"/>
+      <c r="V18" s="13" t="n"/>
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr"/>
+      <c r="A19" s="12" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="8" t="inlineStr"/>
+      <c r="G19" s="13" t="n"/>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
       <c r="K19" s="5" t="n"/>
-      <c r="L19" s="8" t="inlineStr"/>
+      <c r="L19" s="13" t="n"/>
       <c r="M19" s="5" t="n"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="14" t="n"/>
       <c r="O19" s="5" t="n"/>
-      <c r="P19" s="8" t="inlineStr"/>
+      <c r="P19" s="15" t="n"/>
       <c r="Q19" s="5" t="n"/>
       <c r="R19" s="5" t="n"/>
-      <c r="S19" s="8" t="inlineStr"/>
+      <c r="S19" s="10">
+        <f>IF(OR(N19="",P19=""),"",INT(ROUND(N19*P19,6)))</f>
+        <v/>
+      </c>
       <c r="T19" s="5" t="n"/>
       <c r="U19" s="5" t="n"/>
-      <c r="V19" s="8" t="inlineStr"/>
+      <c r="V19" s="13" t="n"/>
       <c r="W19" s="5" t="n"/>
       <c r="X19" s="5" t="n"/>
     </row>
-    <row r="20" ht="6" customHeight="1"/>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>합        계</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="17">
+        <f>SUM(S15:S19)</f>
+        <v/>
+      </c>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="5" t="n"/>
+      <c r="V20" s="16" t="inlineStr"/>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="6" customHeight="1"/>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>매수인(이하 「갑」)과 매도인(이하 「을」)은 위 자재의 매매에 관하여 다음과 같이 계약을 체결한다.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="6" customHeight="1"/>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="23" ht="6" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>제1조 (목적물)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="43.5" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="25" ht="43.5" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>을은 위 표의 자재를 갑이 지정한 장소에 납품하고, 갑은 그 대금을 지급한다.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="4" customHeight="1"/>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="26" ht="4" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>제2조 (납품)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="43.5" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="28" ht="43.5" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>을은 납품 기한까지 자재를 납품한다. 부득이한 사유로 납품이 늦어질 때에는 미리 갑에게 알리고 협의한다.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="4" customHeight="1"/>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="29" ht="4" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>제3조 (검수)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="43.5" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+    <row r="31" ht="43.5" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>갑은 납품 즉시 수량과 규격을 검수한다. 불합격품은 을의 부담으로 반품 또는 교체한다.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="4" customHeight="1"/>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="1" t="inlineStr">
+    <row r="32" ht="4" customHeight="1"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>제4조 (대금의 지급)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="29" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="34" ht="29" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>갑은 검수에 합격한 자재에 대하여 위 지급기한 안에 대금을 지급한다.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="4" customHeight="1"/>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="1" t="inlineStr">
+    <row r="35" ht="4" customHeight="1"/>
+    <row r="36" ht="7.785714285714286" customHeight="1"/>
+    <row r="37" ht="7.785714285714286" customHeight="1"/>
+    <row r="38" ht="7.785714285714286" customHeight="1"/>
+    <row r="39" ht="7.785714285714286" customHeight="1"/>
+    <row r="40" ht="7.785714285714286" customHeight="1"/>
+    <row r="41" ht="7.785714285714286" customHeight="1"/>
+    <row r="42" ht="7.785714285714286" customHeight="1"/>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>제5조 (품질 보증)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="43.5" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="44" ht="43.5" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>을은 납품한 자재가 계약된 규격과 관계 기준에 맞음을 보증하고, 요구가 있으면 시험성적서를 제출한다.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="4" customHeight="1"/>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="1" t="inlineStr">
+    <row r="45" ht="4" customHeight="1"/>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>제6조 (위험 부담)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="43.5" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="47" ht="43.5" customHeight="1">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>납품 완료 및 검수 합격 전까지 자재의 멸실·훼손 위험은 을이 부담한다.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="4" customHeight="1"/>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="1" t="inlineStr">
+    <row r="48" ht="4" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>제7조 (지체)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="43.5" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="50" ht="43.5" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>을의 책임으로 납품이 늦어져 공사에 지장을 준 때에는 그 손해를 배상한다.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="4" customHeight="1"/>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="1" t="inlineStr">
+    <row r="51" ht="4" customHeight="1"/>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>제8조 (분쟁의 해결)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="43.5" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="53" ht="43.5" customHeight="1">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>분쟁은 협의로 해결하되, 협의가 되지 아니한 때에는 관할 법원의 판결에 따른다.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="4" customHeight="1"/>
-    <row r="47" ht="6" customHeight="1"/>
-    <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="54" ht="4" customHeight="1"/>
+    <row r="55" ht="6" customHeight="1"/>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>상호(성명)</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="7" t="inlineStr">
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="11" t="inlineStr">
         <is>
           <t>사업자등록번호</t>
         </is>
       </c>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="n"/>
-      <c r="L48" s="7" t="inlineStr">
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="11" t="inlineStr">
         <is>
           <t>대표자</t>
         </is>
       </c>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="n"/>
-      <c r="O48" s="7" t="inlineStr">
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="n"/>
+      <c r="O56" s="11" t="inlineStr">
         <is>
           <t>주소</t>
         </is>
       </c>
-      <c r="P48" s="5" t="n"/>
-      <c r="Q48" s="5" t="n"/>
-      <c r="R48" s="5" t="n"/>
-      <c r="S48" s="5" t="n"/>
-      <c r="T48" s="5" t="n"/>
-      <c r="U48" s="5" t="n"/>
-      <c r="V48" s="7" t="inlineStr">
+      <c r="P56" s="5" t="n"/>
+      <c r="Q56" s="5" t="n"/>
+      <c r="R56" s="5" t="n"/>
+      <c r="S56" s="5" t="n"/>
+      <c r="T56" s="5" t="n"/>
+      <c r="U56" s="5" t="n"/>
+      <c r="V56" s="11" t="inlineStr">
         <is>
           <t>연락처</t>
         </is>
       </c>
-      <c r="W48" s="5" t="n"/>
-      <c r="X48" s="5" t="n"/>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="8" t="inlineStr"/>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="8" t="inlineStr"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="8" t="inlineStr"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="n"/>
-      <c r="L49" s="8" t="inlineStr"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="n"/>
-      <c r="O49" s="8" t="inlineStr"/>
-      <c r="P49" s="5" t="n"/>
-      <c r="Q49" s="5" t="n"/>
-      <c r="R49" s="5" t="n"/>
-      <c r="S49" s="5" t="n"/>
-      <c r="T49" s="5" t="n"/>
-      <c r="U49" s="5" t="n"/>
-      <c r="V49" s="8" t="inlineStr"/>
-      <c r="W49" s="5" t="n"/>
-      <c r="X49" s="5" t="n"/>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="8" t="inlineStr"/>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="8" t="inlineStr"/>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="n"/>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="8" t="inlineStr"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
-      <c r="L50" s="8" t="inlineStr"/>
-      <c r="M50" s="5" t="n"/>
-      <c r="N50" s="5" t="n"/>
-      <c r="O50" s="8" t="inlineStr"/>
-      <c r="P50" s="5" t="n"/>
-      <c r="Q50" s="5" t="n"/>
-      <c r="R50" s="5" t="n"/>
-      <c r="S50" s="5" t="n"/>
-      <c r="T50" s="5" t="n"/>
-      <c r="U50" s="5" t="n"/>
-      <c r="V50" s="8" t="inlineStr"/>
-      <c r="W50" s="5" t="n"/>
-      <c r="X50" s="5" t="n"/>
-    </row>
-    <row r="51" ht="6" customHeight="1"/>
-    <row r="52" ht="26" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="W56" s="5" t="n"/>
+      <c r="X56" s="5" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>갑</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="13" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="13" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="13" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="n"/>
+      <c r="O57" s="12" t="n"/>
+      <c r="P57" s="5" t="n"/>
+      <c r="Q57" s="5" t="n"/>
+      <c r="R57" s="5" t="n"/>
+      <c r="S57" s="5" t="n"/>
+      <c r="T57" s="5" t="n"/>
+      <c r="U57" s="5" t="n"/>
+      <c r="V57" s="13" t="n"/>
+      <c r="W57" s="5" t="n"/>
+      <c r="X57" s="5" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>을</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="13" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="13" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="13" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="n"/>
+      <c r="O58" s="12" t="n"/>
+      <c r="P58" s="5" t="n"/>
+      <c r="Q58" s="5" t="n"/>
+      <c r="R58" s="5" t="n"/>
+      <c r="S58" s="5" t="n"/>
+      <c r="T58" s="5" t="n"/>
+      <c r="U58" s="5" t="n"/>
+      <c r="V58" s="13" t="n"/>
+      <c r="W58" s="5" t="n"/>
+      <c r="X58" s="5" t="n"/>
+    </row>
+    <row r="59" ht="6" customHeight="1"/>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="18" t="inlineStr">
         <is>
           <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="6" customHeight="1"/>
-    <row r="54" ht="10" customHeight="1"/>
-    <row r="55" ht="26" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="K56" s="12" t="inlineStr">
+    <row r="61" ht="6" customHeight="1"/>
+    <row r="62" ht="10" customHeight="1"/>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="22" t="inlineStr"/>
+      <c r="K64" s="23" t="inlineStr">
         <is>
           <t>갑 (매수인)</t>
         </is>
       </c>
-      <c r="S56" s="11" t="inlineStr">
+      <c r="Q64" s="24" t="n"/>
+      <c r="U64" s="25" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="K57" s="12" t="inlineStr">
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="22" t="inlineStr"/>
+      <c r="K65" s="23" t="inlineStr">
         <is>
           <t>을 (매도인)</t>
         </is>
       </c>
-      <c r="S57" s="11" t="inlineStr">
+      <c r="Q65" s="24" t="n"/>
+      <c r="U65" s="25" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="6" customHeight="1"/>
-    <row r="61">
-      <c r="A61" s="13" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="66" ht="6" customHeight="1"/>
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="26" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="A69" s="26" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="103">
+  <mergeCells count="112">
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="S14:U14"/>
+    <mergeCell ref="O58:U58"/>
+    <mergeCell ref="A69:X69"/>
+    <mergeCell ref="C58:G58"/>
     <mergeCell ref="G10:X10"/>
     <mergeCell ref="P17:R17"/>
     <mergeCell ref="L19:M19"/>
-    <mergeCell ref="V49:X49"/>
+    <mergeCell ref="L58:N58"/>
     <mergeCell ref="A3:X3"/>
-    <mergeCell ref="A55:X55"/>
     <mergeCell ref="S15:U15"/>
     <mergeCell ref="P19:R19"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A32:X32"/>
+    <mergeCell ref="A56:B56"/>
     <mergeCell ref="L14:M14"/>
     <mergeCell ref="N14:O14"/>
-    <mergeCell ref="V50:X50"/>
-    <mergeCell ref="A29:X29"/>
+    <mergeCell ref="U65:X65"/>
     <mergeCell ref="G15:K15"/>
-    <mergeCell ref="A38:X38"/>
+    <mergeCell ref="K65:P65"/>
     <mergeCell ref="P14:R14"/>
-    <mergeCell ref="L48:N48"/>
+    <mergeCell ref="Q64:T64"/>
+    <mergeCell ref="A31:X31"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="G12:X12"/>
     <mergeCell ref="V14:X14"/>
     <mergeCell ref="N15:O15"/>
     <mergeCell ref="A24:X24"/>
     <mergeCell ref="G16:K16"/>
+    <mergeCell ref="A60:X60"/>
+    <mergeCell ref="C57:G57"/>
     <mergeCell ref="S17:U17"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="O56:U56"/>
     <mergeCell ref="G7:X7"/>
     <mergeCell ref="L16:M16"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="S57:X57"/>
+    <mergeCell ref="A25:X25"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="K9:X9"/>
     <mergeCell ref="P16:R16"/>
-    <mergeCell ref="L50:N50"/>
-    <mergeCell ref="A42:X42"/>
+    <mergeCell ref="A50:X50"/>
+    <mergeCell ref="O57:U57"/>
     <mergeCell ref="P18:R18"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="L49:N49"/>
+    <mergeCell ref="A47:X47"/>
+    <mergeCell ref="A22:X22"/>
+    <mergeCell ref="V57:X57"/>
+    <mergeCell ref="H56:K56"/>
     <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A28:X28"/>
     <mergeCell ref="G14:K14"/>
-    <mergeCell ref="G9:X9"/>
     <mergeCell ref="V17:X17"/>
     <mergeCell ref="A44:X44"/>
-    <mergeCell ref="H49:K49"/>
     <mergeCell ref="S16:U16"/>
-    <mergeCell ref="C48:G48"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A30:X30"/>
+    <mergeCell ref="V58:X58"/>
     <mergeCell ref="G11:X11"/>
     <mergeCell ref="S18:U18"/>
-    <mergeCell ref="O50:U50"/>
-    <mergeCell ref="A61:X61"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A41:X41"/>
-    <mergeCell ref="O48:U48"/>
-    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="K64:P64"/>
+    <mergeCell ref="V20:X20"/>
+    <mergeCell ref="Q65:T65"/>
     <mergeCell ref="V15:X15"/>
     <mergeCell ref="G17:K17"/>
     <mergeCell ref="A27:X27"/>
-    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="G9:J9"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="L18:M18"/>
     <mergeCell ref="A33:X33"/>
     <mergeCell ref="N18:O18"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="G19:K19"/>
+    <mergeCell ref="A64:J64"/>
+    <mergeCell ref="L56:N56"/>
+    <mergeCell ref="S20:U20"/>
     <mergeCell ref="V16:X16"/>
     <mergeCell ref="N17:O17"/>
-    <mergeCell ref="K56:R56"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A35:X35"/>
+    <mergeCell ref="A53:X53"/>
+    <mergeCell ref="H58:K58"/>
     <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A68:X68"/>
     <mergeCell ref="V18:X18"/>
     <mergeCell ref="N19:O19"/>
-    <mergeCell ref="O49:U49"/>
-    <mergeCell ref="A39:X39"/>
-    <mergeCell ref="A45:X45"/>
+    <mergeCell ref="L57:N57"/>
+    <mergeCell ref="H57:K57"/>
     <mergeCell ref="V19:X19"/>
+    <mergeCell ref="U64:X64"/>
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A21:X21"/>
+    <mergeCell ref="A46:X46"/>
     <mergeCell ref="S19:U19"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A26:X26"/>
     <mergeCell ref="G5:X5"/>
     <mergeCell ref="L15:M15"/>
-    <mergeCell ref="A23:X23"/>
     <mergeCell ref="G18:K18"/>
-    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="A20:R20"/>
     <mergeCell ref="P15:R15"/>
+    <mergeCell ref="A43:X43"/>
     <mergeCell ref="A52:X52"/>
-    <mergeCell ref="S56:X56"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="A63:X63"/>
+    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A34:X34"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="V48:X48"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="K57:R57"/>
+    <mergeCell ref="A49:X49"/>
     <mergeCell ref="M1:X1"/>
-    <mergeCell ref="A36:X36"/>
+    <mergeCell ref="A58:B58"/>
     <mergeCell ref="G8:X8"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="N15:N19">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(ISNUMBER(N15),MOD(N15,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>자 재 구 매 계 약 서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공 사 명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  납품 장소</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>가나시 다라동 123-4 현장 야적장</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  납품 기한</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="7" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  계약금액</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="8">
+        <f>IF(SUM(S15:S19)=0,"",SUM(S15:S19)+K9)</f>
+        <v/>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  부가가치세</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="10">
+        <f>IF(SUM(S15:S19)=0,"",INT(ROUND(SUM(S15:S19)*G9,6)))</f>
+        <v/>
+      </c>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  운반비 부담</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>매도인(을)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="5" t="n"/>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  하차비 부담</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>매수인(갑) — 현장 장비로 하차</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="5" t="n"/>
+      <c r="V11" s="5" t="n"/>
+      <c r="W11" s="5" t="n"/>
+      <c r="X11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  대금 지급기한</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>납품·검수 후 30일 안</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="5" t="n"/>
+      <c r="V12" s="5" t="n"/>
+      <c r="W12" s="5" t="n"/>
+      <c r="X12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="6" customHeight="1"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>품명</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>규격</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="11" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="n"/>
+      <c r="U14" s="5" t="n"/>
+      <c r="V14" s="11" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="n"/>
+      <c r="X14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>PE 이중벽관</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>D600, L=6m</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="15" t="n">
+        <v>98500</v>
+      </c>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="10">
+        <f>IF(OR(N15="",P15=""),"",INT(ROUND(N15*P15,6)))</f>
+        <v/>
+      </c>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="5" t="n"/>
+      <c r="V15" s="13" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>고무링</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>D600</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="15" t="n">
+        <v>12300</v>
+      </c>
+      <c r="Q16" s="5" t="n"/>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="10">
+        <f>IF(OR(N16="",P16=""),"",INT(ROUND(N16*P16,6)))</f>
+        <v/>
+      </c>
+      <c r="T16" s="5" t="n"/>
+      <c r="U16" s="5" t="n"/>
+      <c r="V16" s="13" t="n"/>
+      <c r="W16" s="5" t="n"/>
+      <c r="X16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="12" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="13" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="15" t="n"/>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="10">
+        <f>IF(OR(N17="",P17=""),"",INT(ROUND(N17*P17,6)))</f>
+        <v/>
+      </c>
+      <c r="T17" s="5" t="n"/>
+      <c r="U17" s="5" t="n"/>
+      <c r="V17" s="13" t="n"/>
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="12" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="14" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="10">
+        <f>IF(OR(N18="",P18=""),"",INT(ROUND(N18*P18,6)))</f>
+        <v/>
+      </c>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="5" t="n"/>
+      <c r="V18" s="13" t="n"/>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="12" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="14" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="15" t="n"/>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="10">
+        <f>IF(OR(N19="",P19=""),"",INT(ROUND(N19*P19,6)))</f>
+        <v/>
+      </c>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="5" t="n"/>
+      <c r="V19" s="13" t="n"/>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>합        계</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="17">
+        <f>SUM(S15:S19)</f>
+        <v/>
+      </c>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="5" t="n"/>
+      <c r="V20" s="16" t="inlineStr"/>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="6" customHeight="1"/>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>매수인(이하 「갑」)과 매도인(이하 「을」)은 위 자재의 매매에 관하여 다음과 같이 계약을 체결한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="6" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>제1조 (목적물)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="43.5" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>을은 위 표의 자재를 갑이 지정한 장소에 납품하고, 갑은 그 대금을 지급한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="4" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>제2조 (납품)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="43.5" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>을은 납품 기한까지 자재를 납품한다. 부득이한 사유로 납품이 늦어질 때에는 미리 갑에게 알리고 협의한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="4" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>제3조 (검수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="43.5" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>갑은 납품 즉시 수량과 규격을 검수한다. 불합격품은 을의 부담으로 반품 또는 교체한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="4" customHeight="1"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>제4조 (대금의 지급)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="29" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>갑은 검수에 합격한 자재에 대하여 위 지급기한 안에 대금을 지급한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="4" customHeight="1"/>
+    <row r="36" ht="7.785714285714286" customHeight="1"/>
+    <row r="37" ht="7.785714285714286" customHeight="1"/>
+    <row r="38" ht="7.785714285714286" customHeight="1"/>
+    <row r="39" ht="7.785714285714286" customHeight="1"/>
+    <row r="40" ht="7.785714285714286" customHeight="1"/>
+    <row r="41" ht="7.785714285714286" customHeight="1"/>
+    <row r="42" ht="7.785714285714286" customHeight="1"/>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>제5조 (품질 보증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="43.5" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>을은 납품한 자재가 계약된 규격과 관계 기준에 맞음을 보증하고, 요구가 있으면 시험성적서를 제출한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="4" customHeight="1"/>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>제6조 (위험 부담)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="43.5" customHeight="1">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>납품 완료 및 검수 합격 전까지 자재의 멸실·훼손 위험은 을이 부담한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="4" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>제7조 (지체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="43.5" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>을의 책임으로 납품이 늦어져 공사에 지장을 준 때에는 그 손해를 배상한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="4" customHeight="1"/>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>제8조 (분쟁의 해결)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="43.5" customHeight="1">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>분쟁은 협의로 해결하되, 협의가 되지 아니한 때에는 관할 법원의 판결에 따른다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="4" customHeight="1"/>
+    <row r="55" ht="6" customHeight="1"/>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>상호(성명)</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>사업자등록번호</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="11" t="inlineStr">
+        <is>
+          <t>대표자</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="n"/>
+      <c r="O56" s="11" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="P56" s="5" t="n"/>
+      <c r="Q56" s="5" t="n"/>
+      <c r="R56" s="5" t="n"/>
+      <c r="S56" s="5" t="n"/>
+      <c r="T56" s="5" t="n"/>
+      <c r="U56" s="5" t="n"/>
+      <c r="V56" s="11" t="inlineStr">
+        <is>
+          <t>연락처</t>
+        </is>
+      </c>
+      <c r="W56" s="5" t="n"/>
+      <c r="X56" s="5" t="n"/>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>갑</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>예시건설(주)</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>000-00-00000</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="13" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="n"/>
+      <c r="O57" s="12" t="inlineStr">
+        <is>
+          <t>가나시 마바로 45, 2층</t>
+        </is>
+      </c>
+      <c r="P57" s="5" t="n"/>
+      <c r="Q57" s="5" t="n"/>
+      <c r="R57" s="5" t="n"/>
+      <c r="S57" s="5" t="n"/>
+      <c r="T57" s="5" t="n"/>
+      <c r="U57" s="5" t="n"/>
+      <c r="V57" s="13" t="inlineStr">
+        <is>
+          <t>000-000-0000</t>
+        </is>
+      </c>
+      <c r="W57" s="5" t="n"/>
+      <c r="X57" s="5" t="n"/>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>을</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>예시관산업(주)</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
+          <t>000-00-00000</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="13" t="inlineStr">
+        <is>
+          <t>관대표</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="n"/>
+      <c r="O58" s="12" t="inlineStr">
+        <is>
+          <t>가나시 산단로 21</t>
+        </is>
+      </c>
+      <c r="P58" s="5" t="n"/>
+      <c r="Q58" s="5" t="n"/>
+      <c r="R58" s="5" t="n"/>
+      <c r="S58" s="5" t="n"/>
+      <c r="T58" s="5" t="n"/>
+      <c r="U58" s="5" t="n"/>
+      <c r="V58" s="13" t="inlineStr">
+        <is>
+          <t>000-000-0000</t>
+        </is>
+      </c>
+      <c r="W58" s="5" t="n"/>
+      <c r="X58" s="5" t="n"/>
+    </row>
+    <row r="59" ht="6" customHeight="1"/>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="6" customHeight="1"/>
+    <row r="62" ht="10" customHeight="1"/>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="21" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="22" t="inlineStr"/>
+      <c r="K64" s="23" t="inlineStr">
+        <is>
+          <t>갑 (매수인)</t>
+        </is>
+      </c>
+      <c r="Q64" s="24" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="U64" s="25" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="22" t="inlineStr"/>
+      <c r="K65" s="23" t="inlineStr">
+        <is>
+          <t>을 (매도인)</t>
+        </is>
+      </c>
+      <c r="Q65" s="24" t="inlineStr">
+        <is>
+          <t>관대표</t>
+        </is>
+      </c>
+      <c r="U65" s="25" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="6" customHeight="1"/>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="A68" s="26" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="111">
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="S14:U14"/>
+    <mergeCell ref="O58:U58"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="G10:X10"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L58:N58"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="S15:U15"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="U65:X65"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="K65:P65"/>
+    <mergeCell ref="P14:R14"/>
+    <mergeCell ref="Q64:T64"/>
+    <mergeCell ref="A31:X31"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="G12:X12"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="A24:X24"/>
+    <mergeCell ref="G16:K16"/>
+    <mergeCell ref="A60:X60"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="S17:U17"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="O56:U56"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="A25:X25"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="K9:X9"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="A50:X50"/>
+    <mergeCell ref="O57:U57"/>
+    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="A47:X47"/>
+    <mergeCell ref="A22:X22"/>
+    <mergeCell ref="V57:X57"/>
+    <mergeCell ref="H56:K56"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A28:X28"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="V17:X17"/>
+    <mergeCell ref="A44:X44"/>
+    <mergeCell ref="S16:U16"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A30:X30"/>
+    <mergeCell ref="V58:X58"/>
+    <mergeCell ref="G11:X11"/>
+    <mergeCell ref="S18:U18"/>
+    <mergeCell ref="K64:P64"/>
+    <mergeCell ref="V20:X20"/>
+    <mergeCell ref="Q65:T65"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="G17:K17"/>
+    <mergeCell ref="A27:X27"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="A33:X33"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="G19:K19"/>
+    <mergeCell ref="A64:J64"/>
+    <mergeCell ref="L56:N56"/>
+    <mergeCell ref="S20:U20"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A53:X53"/>
+    <mergeCell ref="H58:K58"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A68:X68"/>
+    <mergeCell ref="V18:X18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="L57:N57"/>
+    <mergeCell ref="H57:K57"/>
+    <mergeCell ref="V19:X19"/>
+    <mergeCell ref="U64:X64"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A46:X46"/>
+    <mergeCell ref="S19:U19"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="A20:R20"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="A43:X43"/>
+    <mergeCell ref="A52:X52"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="A63:X63"/>
+    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A34:X34"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A49:X49"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="G8:X8"/>
+  </mergeCells>
+  <conditionalFormatting sqref="N15:N19">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(ISNUMBER(N15),MOD(N15,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/gy-jajae.xlsx
+++ b/web/public/forms/gy-jajae.xlsx
@@ -634,7 +634,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="27" t="inlineStr">

--- a/web/public/forms/gy-jajae.xlsx
+++ b/web/public/forms/gy-jajae.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자재 구매계약서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'자재 구매계약서'!$A$1:$X$66</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -151,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -228,19 +226,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <numFmt numFmtId="300" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -753,10 +743,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="8">
-        <f>IF(SUM(S15:S19)=0,"",SUM(S15:S19)+K9)</f>
-        <v/>
-      </c>
+      <c r="G8" s="8" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -792,10 +779,7 @@
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
-      <c r="K9" s="10">
-        <f>IF(SUM(S15:S19)=0,"",INT(ROUND(SUM(S15:S19)*G9,6)))</f>
-        <v/>
-      </c>
+      <c r="K9" s="10" t="n"/>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="5" t="n"/>
       <c r="N9" s="5" t="n"/>
@@ -974,10 +958,7 @@
       <c r="P15" s="15" t="n"/>
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
-      <c r="S15" s="10">
-        <f>IF(OR(N15="",P15=""),"",INT(ROUND(N15*P15,6)))</f>
-        <v/>
-      </c>
+      <c r="S15" s="10" t="n"/>
       <c r="T15" s="5" t="n"/>
       <c r="U15" s="5" t="n"/>
       <c r="V15" s="13" t="n"/>
@@ -1003,10 +984,7 @@
       <c r="P16" s="15" t="n"/>
       <c r="Q16" s="5" t="n"/>
       <c r="R16" s="5" t="n"/>
-      <c r="S16" s="10">
-        <f>IF(OR(N16="",P16=""),"",INT(ROUND(N16*P16,6)))</f>
-        <v/>
-      </c>
+      <c r="S16" s="10" t="n"/>
       <c r="T16" s="5" t="n"/>
       <c r="U16" s="5" t="n"/>
       <c r="V16" s="13" t="n"/>
@@ -1032,10 +1010,7 @@
       <c r="P17" s="15" t="n"/>
       <c r="Q17" s="5" t="n"/>
       <c r="R17" s="5" t="n"/>
-      <c r="S17" s="10">
-        <f>IF(OR(N17="",P17=""),"",INT(ROUND(N17*P17,6)))</f>
-        <v/>
-      </c>
+      <c r="S17" s="10" t="n"/>
       <c r="T17" s="5" t="n"/>
       <c r="U17" s="5" t="n"/>
       <c r="V17" s="13" t="n"/>
@@ -1061,10 +1036,7 @@
       <c r="P18" s="15" t="n"/>
       <c r="Q18" s="5" t="n"/>
       <c r="R18" s="5" t="n"/>
-      <c r="S18" s="10">
-        <f>IF(OR(N18="",P18=""),"",INT(ROUND(N18*P18,6)))</f>
-        <v/>
-      </c>
+      <c r="S18" s="10" t="n"/>
       <c r="T18" s="5" t="n"/>
       <c r="U18" s="5" t="n"/>
       <c r="V18" s="13" t="n"/>
@@ -1090,10 +1062,7 @@
       <c r="P19" s="15" t="n"/>
       <c r="Q19" s="5" t="n"/>
       <c r="R19" s="5" t="n"/>
-      <c r="S19" s="10">
-        <f>IF(OR(N19="",P19=""),"",INT(ROUND(N19*P19,6)))</f>
-        <v/>
-      </c>
+      <c r="S19" s="10" t="n"/>
       <c r="T19" s="5" t="n"/>
       <c r="U19" s="5" t="n"/>
       <c r="V19" s="13" t="n"/>
@@ -1123,10 +1092,7 @@
       <c r="P20" s="5" t="n"/>
       <c r="Q20" s="5" t="n"/>
       <c r="R20" s="5" t="n"/>
-      <c r="S20" s="17">
-        <f>SUM(S15:S19)</f>
-        <v/>
-      </c>
+      <c r="S20" s="17" t="n"/>
       <c r="T20" s="5" t="n"/>
       <c r="U20" s="5" t="n"/>
       <c r="V20" s="16" t="inlineStr"/>
@@ -1426,6 +1392,7 @@
       </c>
     </row>
     <row r="66" ht="6" customHeight="1"/>
+    <row r="67"/>
     <row r="68" ht="34" customHeight="1">
       <c r="A68" s="26" t="inlineStr">
         <is>
@@ -1555,1074 +1522,6 @@
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="G8:X8"/>
   </mergeCells>
-  <conditionalFormatting sqref="N15:N19">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(ISNUMBER(N15),MOD(N15,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>자 재 구 매 계 약 서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  납품 장소</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>가나시 다라동 123-4 현장 야적장</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  납품 기한</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="7" t="n">
-        <v>46310</v>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  계약금액</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="8">
-        <f>IF(SUM(S15:S19)=0,"",SUM(S15:S19)+K9)</f>
-        <v/>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  부가가치세</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="10">
-        <f>IF(SUM(S15:S19)=0,"",INT(ROUND(SUM(S15:S19)*G9,6)))</f>
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  운반비 부담</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>매도인(을)</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n"/>
-      <c r="T10" s="5" t="n"/>
-      <c r="U10" s="5" t="n"/>
-      <c r="V10" s="5" t="n"/>
-      <c r="W10" s="5" t="n"/>
-      <c r="X10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  하차비 부담</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>매수인(갑) — 현장 장비로 하차</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="5" t="n"/>
-      <c r="T11" s="5" t="n"/>
-      <c r="U11" s="5" t="n"/>
-      <c r="V11" s="5" t="n"/>
-      <c r="W11" s="5" t="n"/>
-      <c r="X11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  대금 지급기한</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>납품·검수 후 30일 안</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n"/>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="5" t="n"/>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="6" customHeight="1"/>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>품명</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>규격</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>단위</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>단가</t>
-        </is>
-      </c>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="11" t="inlineStr">
-        <is>
-          <t>금액</t>
-        </is>
-      </c>
-      <c r="T14" s="5" t="n"/>
-      <c r="U14" s="5" t="n"/>
-      <c r="V14" s="11" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="W14" s="5" t="n"/>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>PE 이중벽관</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>D600, L=6m</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="13" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="15" t="n">
-        <v>98500</v>
-      </c>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="10">
-        <f>IF(OR(N15="",P15=""),"",INT(ROUND(N15*P15,6)))</f>
-        <v/>
-      </c>
-      <c r="T15" s="5" t="n"/>
-      <c r="U15" s="5" t="n"/>
-      <c r="V15" s="13" t="n"/>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>고무링</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>D600</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="13" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="14" t="n">
-        <v>42</v>
-      </c>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="15" t="n">
-        <v>12300</v>
-      </c>
-      <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="10">
-        <f>IF(OR(N16="",P16=""),"",INT(ROUND(N16*P16,6)))</f>
-        <v/>
-      </c>
-      <c r="T16" s="5" t="n"/>
-      <c r="U16" s="5" t="n"/>
-      <c r="V16" s="13" t="n"/>
-      <c r="W16" s="5" t="n"/>
-      <c r="X16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="13" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="14" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="15" t="n"/>
-      <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="10">
-        <f>IF(OR(N17="",P17=""),"",INT(ROUND(N17*P17,6)))</f>
-        <v/>
-      </c>
-      <c r="T17" s="5" t="n"/>
-      <c r="U17" s="5" t="n"/>
-      <c r="V17" s="13" t="n"/>
-      <c r="W17" s="5" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="13" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="14" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="15" t="n"/>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="10">
-        <f>IF(OR(N18="",P18=""),"",INT(ROUND(N18*P18,6)))</f>
-        <v/>
-      </c>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="5" t="n"/>
-      <c r="V18" s="13" t="n"/>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="13" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="14" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="15" t="n"/>
-      <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="10">
-        <f>IF(OR(N19="",P19=""),"",INT(ROUND(N19*P19,6)))</f>
-        <v/>
-      </c>
-      <c r="T19" s="5" t="n"/>
-      <c r="U19" s="5" t="n"/>
-      <c r="V19" s="13" t="n"/>
-      <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>합        계</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="17">
-        <f>SUM(S15:S19)</f>
-        <v/>
-      </c>
-      <c r="T20" s="5" t="n"/>
-      <c r="U20" s="5" t="n"/>
-      <c r="V20" s="16" t="inlineStr"/>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="6" customHeight="1"/>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>매수인(이하 「갑」)과 매도인(이하 「을」)은 위 자재의 매매에 관하여 다음과 같이 계약을 체결한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="6" customHeight="1"/>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>제1조 (목적물)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="43.5" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>을은 위 표의 자재를 갑이 지정한 장소에 납품하고, 갑은 그 대금을 지급한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="4" customHeight="1"/>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>제2조 (납품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="43.5" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>을은 납품 기한까지 자재를 납품한다. 부득이한 사유로 납품이 늦어질 때에는 미리 갑에게 알리고 협의한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="4" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>제3조 (검수)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="43.5" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>갑은 납품 즉시 수량과 규격을 검수한다. 불합격품은 을의 부담으로 반품 또는 교체한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="4" customHeight="1"/>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>제4조 (대금의 지급)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="29" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>갑은 검수에 합격한 자재에 대하여 위 지급기한 안에 대금을 지급한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="4" customHeight="1"/>
-    <row r="36" ht="7.785714285714286" customHeight="1"/>
-    <row r="37" ht="7.785714285714286" customHeight="1"/>
-    <row r="38" ht="7.785714285714286" customHeight="1"/>
-    <row r="39" ht="7.785714285714286" customHeight="1"/>
-    <row r="40" ht="7.785714285714286" customHeight="1"/>
-    <row r="41" ht="7.785714285714286" customHeight="1"/>
-    <row r="42" ht="7.785714285714286" customHeight="1"/>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
-        <is>
-          <t>제5조 (품질 보증)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="43.5" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>을은 납품한 자재가 계약된 규격과 관계 기준에 맞음을 보증하고, 요구가 있으면 시험성적서를 제출한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="4" customHeight="1"/>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="19" t="inlineStr">
-        <is>
-          <t>제6조 (위험 부담)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="43.5" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>납품 완료 및 검수 합격 전까지 자재의 멸실·훼손 위험은 을이 부담한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="4" customHeight="1"/>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>제7조 (지체)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="43.5" customHeight="1">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>을의 책임으로 납품이 늦어져 공사에 지장을 준 때에는 그 손해를 배상한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="4" customHeight="1"/>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="19" t="inlineStr">
-        <is>
-          <t>제8조 (분쟁의 해결)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="43.5" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
-        <is>
-          <t>분쟁은 협의로 해결하되, 협의가 되지 아니한 때에는 관할 법원의 판결에 따른다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="4" customHeight="1"/>
-    <row r="55" ht="6" customHeight="1"/>
-    <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="11" t="inlineStr">
-        <is>
-          <t>상호(성명)</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="n"/>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="11" t="inlineStr">
-        <is>
-          <t>사업자등록번호</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
-      <c r="L56" s="11" t="inlineStr">
-        <is>
-          <t>대표자</t>
-        </is>
-      </c>
-      <c r="M56" s="5" t="n"/>
-      <c r="N56" s="5" t="n"/>
-      <c r="O56" s="11" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="P56" s="5" t="n"/>
-      <c r="Q56" s="5" t="n"/>
-      <c r="R56" s="5" t="n"/>
-      <c r="S56" s="5" t="n"/>
-      <c r="T56" s="5" t="n"/>
-      <c r="U56" s="5" t="n"/>
-      <c r="V56" s="11" t="inlineStr">
-        <is>
-          <t>연락처</t>
-        </is>
-      </c>
-      <c r="W56" s="5" t="n"/>
-      <c r="X56" s="5" t="n"/>
-    </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="13" t="inlineStr">
-        <is>
-          <t>갑</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="13" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="13" t="inlineStr">
-        <is>
-          <t>000-00-00000</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
-      <c r="L57" s="13" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="M57" s="5" t="n"/>
-      <c r="N57" s="5" t="n"/>
-      <c r="O57" s="12" t="inlineStr">
-        <is>
-          <t>가나시 마바로 45, 2층</t>
-        </is>
-      </c>
-      <c r="P57" s="5" t="n"/>
-      <c r="Q57" s="5" t="n"/>
-      <c r="R57" s="5" t="n"/>
-      <c r="S57" s="5" t="n"/>
-      <c r="T57" s="5" t="n"/>
-      <c r="U57" s="5" t="n"/>
-      <c r="V57" s="13" t="inlineStr">
-        <is>
-          <t>000-000-0000</t>
-        </is>
-      </c>
-      <c r="W57" s="5" t="n"/>
-      <c r="X57" s="5" t="n"/>
-    </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>을</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="n"/>
-      <c r="C58" s="13" t="inlineStr">
-        <is>
-          <t>예시관산업(주)</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="n"/>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="13" t="inlineStr">
-        <is>
-          <t>000-00-00000</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="n"/>
-      <c r="L58" s="13" t="inlineStr">
-        <is>
-          <t>관대표</t>
-        </is>
-      </c>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="n"/>
-      <c r="O58" s="12" t="inlineStr">
-        <is>
-          <t>가나시 산단로 21</t>
-        </is>
-      </c>
-      <c r="P58" s="5" t="n"/>
-      <c r="Q58" s="5" t="n"/>
-      <c r="R58" s="5" t="n"/>
-      <c r="S58" s="5" t="n"/>
-      <c r="T58" s="5" t="n"/>
-      <c r="U58" s="5" t="n"/>
-      <c r="V58" s="13" t="inlineStr">
-        <is>
-          <t>000-000-0000</t>
-        </is>
-      </c>
-      <c r="W58" s="5" t="n"/>
-      <c r="X58" s="5" t="n"/>
-    </row>
-    <row r="59" ht="6" customHeight="1"/>
-    <row r="60" ht="34" customHeight="1">
-      <c r="A60" s="18" t="inlineStr">
-        <is>
-          <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="6" customHeight="1"/>
-    <row r="62" ht="10" customHeight="1"/>
-    <row r="63" ht="26" customHeight="1">
-      <c r="A63" s="21" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="22" t="inlineStr"/>
-      <c r="K64" s="23" t="inlineStr">
-        <is>
-          <t>갑 (매수인)</t>
-        </is>
-      </c>
-      <c r="Q64" s="24" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="U64" s="25" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="22" t="inlineStr"/>
-      <c r="K65" s="23" t="inlineStr">
-        <is>
-          <t>을 (매도인)</t>
-        </is>
-      </c>
-      <c r="Q65" s="24" t="inlineStr">
-        <is>
-          <t>관대표</t>
-        </is>
-      </c>
-      <c r="U65" s="25" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="6" customHeight="1"/>
-    <row r="68" ht="19.5" customHeight="1">
-      <c r="A68" s="26" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="111">
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="S14:U14"/>
-    <mergeCell ref="O58:U58"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="G10:X10"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L58:N58"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="S15:U15"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="U65:X65"/>
-    <mergeCell ref="G15:K15"/>
-    <mergeCell ref="K65:P65"/>
-    <mergeCell ref="P14:R14"/>
-    <mergeCell ref="Q64:T64"/>
-    <mergeCell ref="A31:X31"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="G12:X12"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="A24:X24"/>
-    <mergeCell ref="G16:K16"/>
-    <mergeCell ref="A60:X60"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="S17:U17"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="O56:U56"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="A25:X25"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="K9:X9"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="A50:X50"/>
-    <mergeCell ref="O57:U57"/>
-    <mergeCell ref="P18:R18"/>
-    <mergeCell ref="A47:X47"/>
-    <mergeCell ref="A22:X22"/>
-    <mergeCell ref="V57:X57"/>
-    <mergeCell ref="H56:K56"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A28:X28"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="A44:X44"/>
-    <mergeCell ref="S16:U16"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A30:X30"/>
-    <mergeCell ref="V58:X58"/>
-    <mergeCell ref="G11:X11"/>
-    <mergeCell ref="S18:U18"/>
-    <mergeCell ref="K64:P64"/>
-    <mergeCell ref="V20:X20"/>
-    <mergeCell ref="Q65:T65"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="G17:K17"/>
-    <mergeCell ref="A27:X27"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="A33:X33"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="G19:K19"/>
-    <mergeCell ref="A64:J64"/>
-    <mergeCell ref="L56:N56"/>
-    <mergeCell ref="S20:U20"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A53:X53"/>
-    <mergeCell ref="H58:K58"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A68:X68"/>
-    <mergeCell ref="V18:X18"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="L57:N57"/>
-    <mergeCell ref="H57:K57"/>
-    <mergeCell ref="V19:X19"/>
-    <mergeCell ref="U64:X64"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A46:X46"/>
-    <mergeCell ref="S19:U19"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="G18:K18"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="A20:R20"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="A43:X43"/>
-    <mergeCell ref="A52:X52"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="A63:X63"/>
-    <mergeCell ref="A65:J65"/>
-    <mergeCell ref="A34:X34"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A49:X49"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="G8:X8"/>
-  </mergeCells>
-  <conditionalFormatting sqref="N15:N19">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(ISNUMBER(N15),MOD(N15,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/web/public/forms/gy-jajae.xlsx
+++ b/web/public/forms/gy-jajae.xlsx
@@ -624,7 +624,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
